--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91494</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128221483</v>
       </c>
       <c r="B2" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128221486</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128221483</v>
+        <v>128221486</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730169</v>
+        <v>730186</v>
       </c>
       <c r="R2" t="n">
-        <v>7121486</v>
+        <v>7121516</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -765,55 +769,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128221486</v>
+        <v>128221483</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartbacken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730186</v>
+        <v>730169</v>
       </c>
       <c r="R3" t="n">
-        <v>7121516</v>
+        <v>7121486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,6 +870,411 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128165971</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>730158</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7121446</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128165972</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>730154</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7121458</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128165973</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>730204</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7121456</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128165930</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartbacken, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>730154</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7121446</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på samma tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24413-2024 artfynd.xlsx
+++ b/artfynd/A 24413-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221486</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128221483</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165971</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165972</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165973</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,8 +1305,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128165930</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>